--- a/artfynd/A 15248-2026 artfynd.xlsx
+++ b/artfynd/A 15248-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430750</v>
+        <v>416332</v>
       </c>
       <c r="B2" t="n">
-        <v>100991</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Myrby, Upl</t>
+          <t>Myrby, 400 m N om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686408</v>
+        <v>686407</v>
       </c>
       <c r="R2" t="n">
-        <v>6671302</v>
+        <v>6671308</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +738,24 @@
           <t>Harg</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>C-ÖST-0517</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>1991-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>1991-06-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ETI: UPPLAND: Östhammars kommun, Hargs s:n. 400 m N om Myrby. 6671319, 1641737, 100m / RUBIN 12I4iSV. 1991-06-26. Leg. Rickard Brock KOM: Det. Anna-Lena Anderberg (enligt etiketten). - Ej originaletikett</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,30 +767,39 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Hellkvist, Anna-Lotta Hellqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Rickard Brock</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430751</v>
+        <v>121430750</v>
       </c>
       <c r="B3" t="n">
-        <v>100991</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686426</v>
+        <v>686408</v>
       </c>
       <c r="R3" t="n">
-        <v>6671243</v>
+        <v>6671302</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,10 +886,107 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Hellkvist, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121430751</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>686426</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6671243</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
